--- a/data/trans_bre/P15A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,43</t>
+          <t>-0,31; 2,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,16</t>
+          <t>-0,75; 2,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,24</t>
+          <t>-0,31; 3,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,31</t>
+          <t>0,98; 4,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 137,13</t>
+          <t>-11,38; 126,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 137,23</t>
+          <t>-24,36; 133,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 155,15</t>
+          <t>-14,09; 157,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,49; 245,73</t>
+          <t>21,17; 249,64</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -1,09</t>
+          <t>-3,78; -1,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,28</t>
+          <t>-1,89; 0,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; -0,1</t>
+          <t>-1,95; -0,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,7</t>
+          <t>-1,25; 0,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,35; -27,58</t>
+          <t>-69,88; -30,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 10,27</t>
+          <t>-51,51; 7,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,43; -1,99</t>
+          <t>-62,36; -3,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 41,42</t>
+          <t>-47,05; 46,99</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,81</t>
+          <t>-3,3; 1,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,12</t>
+          <t>-2,11; 2,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,08</t>
+          <t>-1,66; 2,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,23</t>
+          <t>-1,77; 1,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 81,42</t>
+          <t>-65,77; 81,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,63; 180,44</t>
+          <t>-54,01; 184,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 154,75</t>
+          <t>-54,88; 183,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 145,19</t>
+          <t>-62,99; 141,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; -0,16</t>
+          <t>-1,89; 0,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,7</t>
+          <t>-0,96; 0,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,67</t>
+          <t>-0,9; 0,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,32</t>
+          <t>-0,41; 1,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -4,51</t>
+          <t>-44,44; -0,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 28,77</t>
+          <t>-28,65; 29,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 30,87</t>
+          <t>-30,31; 33,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 81,75</t>
+          <t>-16,5; 71,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>107,03%</t>
+          <t>111,95%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,33</t>
+          <t>-0,36; 2,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,2</t>
+          <t>-0,87; 2,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,23</t>
+          <t>-0,4; 3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,19</t>
+          <t>1,14; 4,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 126,86</t>
+          <t>-12,08; 136,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 133,08</t>
+          <t>-27,87; 117,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 157,18</t>
+          <t>-11,32; 149,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 249,64</t>
+          <t>31,76; 276,45</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-13,19%</t>
+          <t>-17,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -1,22</t>
+          <t>-3,73; -1,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,17</t>
+          <t>-1,95; 0,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; -0,08</t>
+          <t>-1,97; -0,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,78</t>
+          <t>-1,49; 0,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,88; -30,03</t>
+          <t>-68,39; -30,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,51; 7,92</t>
+          <t>-52,68; 9,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,36; -3,99</t>
+          <t>-63,41; -3,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 46,99</t>
+          <t>-47,86; 28,54</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,59</t>
+          <t>-3,11; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,95</t>
+          <t>-1,96; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,25</t>
+          <t>-1,7; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,19</t>
+          <t>-1,58; 1,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 81,25</t>
+          <t>-66,07; 66,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 184,53</t>
+          <t>-54,25; 194,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 183,67</t>
+          <t>-52,68; 170,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,99; 141,36</t>
+          <t>-57,81; 144,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,01</t>
+          <t>-1,83; -0,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,71</t>
+          <t>-0,89; 0,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,72</t>
+          <t>-0,83; 0,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,19</t>
+          <t>-0,42; 1,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,44; -0,01</t>
+          <t>-43,63; -4,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 29,6</t>
+          <t>-27,27; 29,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 33,12</t>
+          <t>-29,02; 34,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 71,49</t>
+          <t>-15,63; 55,96</t>
         </is>
       </c>
     </row>
